--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3130,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113018043</v>
+        <v>113018040</v>
       </c>
       <c r="B25" t="n">
-        <v>90029</v>
+        <v>90063</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3146,21 +3146,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620644</v>
+        <v>620549</v>
       </c>
       <c r="R25" t="n">
-        <v>6907290</v>
+        <v>6907071</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113018045</v>
+        <v>113018041</v>
       </c>
       <c r="B26" t="n">
-        <v>90029</v>
+        <v>90009</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,25 +3244,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620338</v>
+        <v>620629</v>
       </c>
       <c r="R26" t="n">
-        <v>6907443</v>
+        <v>6907066</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113018040</v>
+        <v>113018045</v>
       </c>
       <c r="B27" t="n">
-        <v>90047</v>
+        <v>90045</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620549</v>
+        <v>620338</v>
       </c>
       <c r="R27" t="n">
-        <v>6907071</v>
+        <v>6907443</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113018042</v>
+        <v>113018043</v>
       </c>
       <c r="B28" t="n">
-        <v>90414</v>
+        <v>90045</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,32 +3452,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620606</v>
+        <v>620644</v>
       </c>
       <c r="R28" t="n">
-        <v>6907271</v>
+        <v>6907290</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3512,18 +3514,12 @@
           <t>2023-10-31</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3542,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113018041</v>
+        <v>113018042</v>
       </c>
       <c r="B29" t="n">
-        <v>89993</v>
+        <v>90430</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,38 +3550,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620629</v>
+        <v>620606</v>
       </c>
       <c r="R29" t="n">
-        <v>6907066</v>
+        <v>6907271</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3620,12 +3614,18 @@
           <t>2023-10-31</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2108,7 +2108,7 @@
         <v>112038649</v>
       </c>
       <c r="B15" t="n">
-        <v>91971</v>
+        <v>91981</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2108,7 +2108,7 @@
         <v>112038649</v>
       </c>
       <c r="B15" t="n">
-        <v>91981</v>
+        <v>91993</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2108,7 +2108,7 @@
         <v>112038649</v>
       </c>
       <c r="B15" t="n">
-        <v>91993</v>
+        <v>91994</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2108,7 +2108,7 @@
         <v>112038649</v>
       </c>
       <c r="B15" t="n">
-        <v>91994</v>
+        <v>91997</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2108,7 +2108,7 @@
         <v>112038649</v>
       </c>
       <c r="B15" t="n">
-        <v>91997</v>
+        <v>92003</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3642,6 +3642,778 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127291532</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92601</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Åh, Åh, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>620569</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6907190</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127290459</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92627</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>620682</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6906909</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127290877</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92627</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>620729</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6906963</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127294312</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91615</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>620577</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6907001</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127294328</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>620577</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6907001</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127294306</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91773</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>620577</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6907001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127291750</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Åh, Åh, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>620622</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6907237</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92601</v>
+        <v>92607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92627</v>
+        <v>92633</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92627</v>
+        <v>92633</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92634</v>
+        <v>92638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>92638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>127291750</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B34" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92638</v>
+        <v>92640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92638</v>
+        <v>92640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>127291750</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B33" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B34" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290459</v>
+        <v>127290877</v>
       </c>
       <c r="B31" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,26 +3779,17 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620682</v>
+        <v>620729</v>
       </c>
       <c r="R31" t="n">
-        <v>6906909</v>
+        <v>6906963</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3830,7 +3821,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3840,7 +3831,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,10 +3858,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290877</v>
+        <v>127290459</v>
       </c>
       <c r="B32" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3895,17 +3886,26 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620729</v>
+        <v>620682</v>
       </c>
       <c r="R32" t="n">
-        <v>6906963</v>
+        <v>6906909</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B33" t="n">
-        <v>91634</v>
+        <v>91341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B34" t="n">
-        <v>91338</v>
+        <v>91637</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>127291750</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290877</v>
+        <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,17 +3779,26 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620729</v>
+        <v>620682</v>
       </c>
       <c r="R31" t="n">
-        <v>6906963</v>
+        <v>6906909</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3821,7 +3830,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3831,7 +3840,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3858,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290459</v>
+        <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,26 +3895,17 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620682</v>
+        <v>620729</v>
       </c>
       <c r="R32" t="n">
-        <v>6906909</v>
+        <v>6906963</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91341</v>
+        <v>91645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91637</v>
+        <v>91349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>127291750</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B33" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294328</v>
+        <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294312</v>
+        <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4414,6 +4414,316 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129574923</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>620676</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6907043</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129576405</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>620599</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6906925</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129574821</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>620692</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6907114</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på grov gran, långt ned på stammen med rinnande kåda</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>129576405</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129574821</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>129576405</v>
       </c>
       <c r="B38" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129574821</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>129576405</v>
       </c>
       <c r="B38" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129574821</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>129576405</v>
       </c>
       <c r="B38" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>129576405</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>129576405</v>
       </c>
       <c r="B38" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4622,7 +4622,7 @@
         <v>129574821</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4419,7 +4419,7 @@
         <v>129574923</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>129576405</v>
       </c>
       <c r="B38" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -3647,7 +3647,7 @@
         <v>127291532</v>
       </c>
       <c r="B30" t="n">
-        <v>92633</v>
+        <v>92601</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127290459</v>
       </c>
       <c r="B31" t="n">
-        <v>92659</v>
+        <v>92627</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>127290877</v>
       </c>
       <c r="B32" t="n">
-        <v>92659</v>
+        <v>92627</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>127294312</v>
       </c>
       <c r="B33" t="n">
-        <v>91647</v>
+        <v>91615</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>127294328</v>
       </c>
       <c r="B34" t="n">
-        <v>91351</v>
+        <v>91319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>127294306</v>
       </c>
       <c r="B35" t="n">
-        <v>91805</v>
+        <v>91773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>127291750</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4724,6 +4724,1633 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132627016</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>620553</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6907206</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132627029</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>620619</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6907297</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132627017</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>620567</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6907210</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132627014</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>620542</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6907069</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132627031</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>620645</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6907255</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 50 bladroestter</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132627028</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>620564</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6907355</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132627024</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>620566</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6907351</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132627020</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>620612</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6907283</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132627021</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>620605</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6907280</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132627015</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>620554</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6907215</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>rikligt med ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132627019</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>620612</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6907246</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132627030</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>620634</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6907281</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ca 80 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132627023</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>620566</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6907307</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132627032</v>
+      </c>
+      <c r="B53" t="n">
+        <v>96318</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>620624</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6907248</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132627022</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>620576</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6907314</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132627018</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>620569</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6907223</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>100 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4729,7 +4729,7 @@
         <v>132627016</v>
       </c>
       <c r="B40" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>132627029</v>
       </c>
       <c r="B41" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>132627017</v>
       </c>
       <c r="B42" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>132627014</v>
       </c>
       <c r="B43" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>132627031</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>132627028</v>
       </c>
       <c r="B45" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>132627024</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>132627020</v>
       </c>
       <c r="B47" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5537,48 +5537,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132627021</v>
+        <v>132627015</v>
       </c>
       <c r="B48" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620605</v>
+        <v>620554</v>
       </c>
       <c r="R48" t="n">
-        <v>6907280</v>
+        <v>6907215</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5612,7 +5617,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,53 +5644,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132627015</v>
+        <v>132627021</v>
       </c>
       <c r="B49" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620554</v>
+        <v>620605</v>
       </c>
       <c r="R49" t="n">
-        <v>6907215</v>
+        <v>6907280</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5749,7 +5749,7 @@
         <v>132627019</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>132627030</v>
       </c>
       <c r="B51" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132627023</v>
+        <v>132627032</v>
       </c>
       <c r="B52" t="n">
-        <v>99098</v>
+        <v>96326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620566</v>
+        <v>620624</v>
       </c>
       <c r="R52" t="n">
-        <v>6907307</v>
+        <v>6907248</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6021,11 +6021,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,32 +6047,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132627032</v>
+        <v>132627023</v>
       </c>
       <c r="B53" t="n">
-        <v>96318</v>
+        <v>99106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6087,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620624</v>
+        <v>620566</v>
       </c>
       <c r="R53" t="n">
-        <v>6907248</v>
+        <v>6907307</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6123,6 +6118,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6152,7 +6152,7 @@
         <v>132627022</v>
       </c>
       <c r="B54" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>132627018</v>
       </c>
       <c r="B55" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4729,7 +4729,7 @@
         <v>132627016</v>
       </c>
       <c r="B40" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>132627029</v>
       </c>
       <c r="B41" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4930,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132627017</v>
+        <v>132627014</v>
       </c>
       <c r="B42" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4941,37 +4941,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620567</v>
+        <v>620542</v>
       </c>
       <c r="R42" t="n">
-        <v>6907210</v>
+        <v>6907069</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5027,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132627014</v>
+        <v>132627017</v>
       </c>
       <c r="B43" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,42 +5043,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620542</v>
+        <v>620567</v>
       </c>
       <c r="R43" t="n">
-        <v>6907069</v>
+        <v>6907210</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>132627031</v>
       </c>
       <c r="B44" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>132627028</v>
       </c>
       <c r="B45" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>132627024</v>
       </c>
       <c r="B46" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>132627020</v>
       </c>
       <c r="B47" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5537,53 +5537,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132627015</v>
+        <v>132627021</v>
       </c>
       <c r="B48" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620554</v>
+        <v>620605</v>
       </c>
       <c r="R48" t="n">
-        <v>6907215</v>
+        <v>6907280</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5617,7 +5612,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5644,10 +5639,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132627021</v>
+        <v>132627019</v>
       </c>
       <c r="B49" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5679,10 +5674,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620605</v>
+        <v>620612</v>
       </c>
       <c r="R49" t="n">
-        <v>6907280</v>
+        <v>6907246</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5746,48 +5741,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132627019</v>
+        <v>132627015</v>
       </c>
       <c r="B50" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620612</v>
+        <v>620554</v>
       </c>
       <c r="R50" t="n">
-        <v>6907246</v>
+        <v>6907215</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5851,7 +5851,7 @@
         <v>132627030</v>
       </c>
       <c r="B51" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>132627032</v>
       </c>
       <c r="B52" t="n">
-        <v>96326</v>
+        <v>96336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>132627023</v>
       </c>
       <c r="B53" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>132627022</v>
       </c>
       <c r="B54" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>132627018</v>
       </c>
       <c r="B55" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4729,7 +4729,7 @@
         <v>132627016</v>
       </c>
       <c r="B40" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>132627029</v>
       </c>
       <c r="B41" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4930,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132627014</v>
+        <v>132627017</v>
       </c>
       <c r="B42" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4941,42 +4941,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620542</v>
+        <v>620567</v>
       </c>
       <c r="R42" t="n">
-        <v>6907069</v>
+        <v>6907210</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5032,10 +5027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132627017</v>
+        <v>132627014</v>
       </c>
       <c r="B43" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5043,37 +5038,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620567</v>
+        <v>620542</v>
       </c>
       <c r="R43" t="n">
-        <v>6907210</v>
+        <v>6907069</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>132627031</v>
       </c>
       <c r="B44" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>132627028</v>
       </c>
       <c r="B45" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>132627024</v>
       </c>
       <c r="B46" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>132627020</v>
       </c>
       <c r="B47" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5537,48 +5537,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132627021</v>
+        <v>132627015</v>
       </c>
       <c r="B48" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620605</v>
+        <v>620554</v>
       </c>
       <c r="R48" t="n">
-        <v>6907280</v>
+        <v>6907215</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5612,7 +5617,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,10 +5644,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132627019</v>
+        <v>132627021</v>
       </c>
       <c r="B49" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5674,10 +5679,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620612</v>
+        <v>620605</v>
       </c>
       <c r="R49" t="n">
-        <v>6907246</v>
+        <v>6907280</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5741,53 +5746,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132627015</v>
+        <v>132627019</v>
       </c>
       <c r="B50" t="n">
-        <v>57953</v>
+        <v>99117</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620554</v>
+        <v>620612</v>
       </c>
       <c r="R50" t="n">
-        <v>6907215</v>
+        <v>6907246</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5851,7 +5851,7 @@
         <v>132627030</v>
       </c>
       <c r="B51" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>132627032</v>
       </c>
       <c r="B52" t="n">
-        <v>96336</v>
+        <v>96337</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>132627023</v>
       </c>
       <c r="B53" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>132627022</v>
       </c>
       <c r="B54" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>132627018</v>
       </c>
       <c r="B55" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4729,7 +4729,7 @@
         <v>132627016</v>
       </c>
       <c r="B40" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>132627029</v>
       </c>
       <c r="B41" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>132627031</v>
       </c>
       <c r="B44" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>132627028</v>
       </c>
       <c r="B45" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>132627024</v>
       </c>
       <c r="B46" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>132627020</v>
       </c>
       <c r="B47" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>132627021</v>
       </c>
       <c r="B49" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>132627019</v>
       </c>
       <c r="B50" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>132627030</v>
       </c>
       <c r="B51" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>132627032</v>
       </c>
       <c r="B52" t="n">
-        <v>96337</v>
+        <v>96338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B53" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R53" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B54" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R54" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6254,7 +6254,7 @@
         <v>132627018</v>
       </c>
       <c r="B55" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4930,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132627017</v>
+        <v>132627014</v>
       </c>
       <c r="B42" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4941,37 +4941,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620567</v>
+        <v>620542</v>
       </c>
       <c r="R42" t="n">
-        <v>6907210</v>
+        <v>6907069</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5027,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132627014</v>
+        <v>132627017</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,42 +5043,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620542</v>
+        <v>620567</v>
       </c>
       <c r="R43" t="n">
-        <v>6907069</v>
+        <v>6907210</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5950,32 +5950,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132627032</v>
+        <v>132627023</v>
       </c>
       <c r="B52" t="n">
-        <v>96338</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620624</v>
+        <v>620566</v>
       </c>
       <c r="R52" t="n">
-        <v>6907248</v>
+        <v>6907307</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6021,6 +6021,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6149,7 +6154,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627023</v>
+        <v>132627018</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6184,10 +6189,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620566</v>
+        <v>620569</v>
       </c>
       <c r="R54" t="n">
-        <v>6907307</v>
+        <v>6907223</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6224,7 +6229,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6251,32 +6256,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132627018</v>
+        <v>132627032</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>96338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6286,10 +6291,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620569</v>
+        <v>620624</v>
       </c>
       <c r="R55" t="n">
-        <v>6907223</v>
+        <v>6907248</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6322,11 +6327,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -5950,32 +5950,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132627023</v>
+        <v>132627032</v>
       </c>
       <c r="B52" t="n">
-        <v>99118</v>
+        <v>96338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620566</v>
+        <v>620624</v>
       </c>
       <c r="R52" t="n">
-        <v>6907307</v>
+        <v>6907248</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6021,11 +6021,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,7 +6047,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6087,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R53" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6154,7 +6149,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627018</v>
+        <v>132627022</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6189,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620569</v>
+        <v>620576</v>
       </c>
       <c r="R54" t="n">
-        <v>6907223</v>
+        <v>6907314</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6229,7 +6224,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6256,32 +6251,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132627032</v>
+        <v>132627018</v>
       </c>
       <c r="B55" t="n">
-        <v>96338</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6291,10 +6286,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620624</v>
+        <v>620569</v>
       </c>
       <c r="R55" t="n">
-        <v>6907248</v>
+        <v>6907223</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6327,6 +6322,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4729,7 +4729,7 @@
         <v>132627016</v>
       </c>
       <c r="B40" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>132627029</v>
       </c>
       <c r="B41" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>132627014</v>
       </c>
       <c r="B42" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>132627017</v>
       </c>
       <c r="B43" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>132627031</v>
       </c>
       <c r="B44" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>132627028</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>132627024</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>132627020</v>
       </c>
       <c r="B47" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>132627015</v>
       </c>
       <c r="B48" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>132627021</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>132627019</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>132627030</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>132627032</v>
       </c>
       <c r="B52" t="n">
-        <v>96338</v>
+        <v>96339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B53" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R53" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B54" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R54" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6254,7 +6254,7 @@
         <v>132627018</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -5950,32 +5950,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132627022</v>
+        <v>132627032</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>96348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620576</v>
+        <v>620624</v>
       </c>
       <c r="R52" t="n">
-        <v>6907314</v>
+        <v>6907248</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6021,11 +6021,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6154,7 +6149,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627018</v>
+        <v>132627022</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -6189,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620569</v>
+        <v>620576</v>
       </c>
       <c r="R54" t="n">
-        <v>6907223</v>
+        <v>6907314</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6229,7 +6224,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6256,32 +6251,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132627032</v>
+        <v>132627018</v>
       </c>
       <c r="B55" t="n">
-        <v>96348</v>
+        <v>99130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6291,10 +6286,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620624</v>
+        <v>620569</v>
       </c>
       <c r="R55" t="n">
-        <v>6907248</v>
+        <v>6907223</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6327,6 +6322,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4930,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132627017</v>
+        <v>132627014</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4941,37 +4941,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620567</v>
+        <v>620542</v>
       </c>
       <c r="R42" t="n">
-        <v>6907210</v>
+        <v>6907069</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5027,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132627014</v>
+        <v>132627017</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,42 +5043,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620542</v>
+        <v>620567</v>
       </c>
       <c r="R43" t="n">
-        <v>6907069</v>
+        <v>6907210</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5537,53 +5537,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132627015</v>
+        <v>132627021</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620554</v>
+        <v>620605</v>
       </c>
       <c r="R48" t="n">
-        <v>6907215</v>
+        <v>6907280</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5617,7 +5612,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5644,7 +5639,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132627021</v>
+        <v>132627019</v>
       </c>
       <c r="B49" t="n">
         <v>99130</v>
@@ -5679,10 +5674,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620605</v>
+        <v>620612</v>
       </c>
       <c r="R49" t="n">
-        <v>6907280</v>
+        <v>6907246</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5746,48 +5741,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132627019</v>
+        <v>132627015</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620612</v>
+        <v>620554</v>
       </c>
       <c r="R50" t="n">
-        <v>6907246</v>
+        <v>6907215</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6047,7 +6047,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132627023</v>
+        <v>132627018</v>
       </c>
       <c r="B53" t="n">
         <v>99130</v>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620566</v>
+        <v>620569</v>
       </c>
       <c r="R53" t="n">
-        <v>6907307</v>
+        <v>6907223</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6149,7 +6149,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R54" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6251,7 +6251,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132627018</v>
+        <v>132627022</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620569</v>
+        <v>620576</v>
       </c>
       <c r="R55" t="n">
-        <v>6907223</v>
+        <v>6907314</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4930,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132627014</v>
+        <v>132627017</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4941,42 +4941,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620542</v>
+        <v>620567</v>
       </c>
       <c r="R42" t="n">
-        <v>6907069</v>
+        <v>6907210</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5032,10 +5027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132627017</v>
+        <v>132627014</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5043,37 +5038,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620567</v>
+        <v>620542</v>
       </c>
       <c r="R43" t="n">
-        <v>6907210</v>
+        <v>6907069</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5537,48 +5537,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132627021</v>
+        <v>132627015</v>
       </c>
       <c r="B48" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620605</v>
+        <v>620554</v>
       </c>
       <c r="R48" t="n">
-        <v>6907280</v>
+        <v>6907215</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5612,7 +5617,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,7 +5644,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132627019</v>
+        <v>132627021</v>
       </c>
       <c r="B49" t="n">
         <v>99130</v>
@@ -5674,10 +5679,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620612</v>
+        <v>620605</v>
       </c>
       <c r="R49" t="n">
-        <v>6907246</v>
+        <v>6907280</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5741,53 +5746,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132627015</v>
+        <v>132627019</v>
       </c>
       <c r="B50" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620554</v>
+        <v>620612</v>
       </c>
       <c r="R50" t="n">
-        <v>6907215</v>
+        <v>6907246</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6047,7 +6047,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132627018</v>
+        <v>132627023</v>
       </c>
       <c r="B53" t="n">
         <v>99130</v>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620569</v>
+        <v>620566</v>
       </c>
       <c r="R53" t="n">
-        <v>6907223</v>
+        <v>6907307</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6149,7 +6149,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R54" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6251,7 +6251,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132627022</v>
+        <v>132627018</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620576</v>
+        <v>620569</v>
       </c>
       <c r="R55" t="n">
-        <v>6907314</v>
+        <v>6907223</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -4930,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132627017</v>
+        <v>132627014</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4941,37 +4941,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620567</v>
+        <v>620542</v>
       </c>
       <c r="R42" t="n">
-        <v>6907210</v>
+        <v>6907069</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5027,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132627014</v>
+        <v>132627017</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,42 +5043,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620542</v>
+        <v>620567</v>
       </c>
       <c r="R43" t="n">
-        <v>6907069</v>
+        <v>6907210</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6351,6 +6351,204 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133816706</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79872</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kulåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>620552</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6907124</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133816705</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79872</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kulåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>620550</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6907041</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -6356,7 +6356,7 @@
         <v>133816706</v>
       </c>
       <c r="B56" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>133816705</v>
       </c>
       <c r="B57" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -6356,7 +6356,7 @@
         <v>133816706</v>
       </c>
       <c r="B56" t="n">
-        <v>79873</v>
+        <v>79887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>133816705</v>
       </c>
       <c r="B57" t="n">
-        <v>79873</v>
+        <v>79887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -6356,7 +6356,7 @@
         <v>133816706</v>
       </c>
       <c r="B56" t="n">
-        <v>79887</v>
+        <v>79897</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>133816705</v>
       </c>
       <c r="B57" t="n">
-        <v>79887</v>
+        <v>79897</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -6356,7 +6356,7 @@
         <v>133816706</v>
       </c>
       <c r="B56" t="n">
-        <v>79897</v>
+        <v>79898</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>133816705</v>
       </c>
       <c r="B57" t="n">
-        <v>79897</v>
+        <v>79898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -6356,7 +6356,7 @@
         <v>133816706</v>
       </c>
       <c r="B56" t="n">
-        <v>79898</v>
+        <v>79905</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>133816705</v>
       </c>
       <c r="B57" t="n">
-        <v>79898</v>
+        <v>79905</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102531575</v>
+        <v>127294312</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620531.4755269032</v>
+        <v>620577</v>
       </c>
       <c r="R2" t="n">
-        <v>6907514.646631155</v>
+        <v>6907001</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102531648</v>
+        <v>112038636</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,22 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620615.1458763825</v>
+        <v>620541</v>
       </c>
       <c r="R3" t="n">
-        <v>6907146.777722652</v>
+        <v>6907017</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,57 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102531620</v>
+        <v>127294328</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620661.9301832733</v>
+        <v>620577</v>
       </c>
       <c r="R4" t="n">
-        <v>6907156.380073499</v>
+        <v>6907001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +968,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,57 +986,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102531551</v>
+        <v>129576405</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620512.616854154</v>
+        <v>620599</v>
       </c>
       <c r="R5" t="n">
-        <v>6907416.129813038</v>
+        <v>6906925</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1142,57 +1083,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102531588</v>
+        <v>127294306</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620593.2201437417</v>
+        <v>620577</v>
       </c>
       <c r="R6" t="n">
-        <v>6907289.4990068</v>
+        <v>6907001</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,22 +1148,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1172,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,57 +1190,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102531566</v>
+        <v>112038649</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2058</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620509.3891624246</v>
+        <v>620727</v>
       </c>
       <c r="R7" t="n">
-        <v>6907532.023517531</v>
+        <v>6906958</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,22 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1376,57 +1287,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102531602</v>
+        <v>112038637</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620635.4159901729</v>
+        <v>620638</v>
       </c>
       <c r="R8" t="n">
-        <v>6907257.934034973</v>
+        <v>6906943</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,22 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1366,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1493,15 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112038653</v>
+        <v>112038641</v>
       </c>
       <c r="B9" t="n">
-        <v>90859</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1533,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620699</v>
+        <v>620633</v>
       </c>
       <c r="R9" t="n">
-        <v>6907035</v>
+        <v>6906857</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,37 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112038639</v>
+        <v>112038642</v>
       </c>
       <c r="B10" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620642</v>
+        <v>620645</v>
       </c>
       <c r="R10" t="n">
-        <v>6906939</v>
+        <v>6906829</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1697,15 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112038636</v>
+        <v>112038646</v>
       </c>
       <c r="B11" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620540</v>
+        <v>620674</v>
       </c>
       <c r="R11" t="n">
-        <v>6907018</v>
+        <v>6906876</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1799,37 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112038638</v>
+        <v>112038652</v>
       </c>
       <c r="B12" t="n">
-        <v>103794</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620639</v>
+        <v>620718</v>
       </c>
       <c r="R12" t="n">
-        <v>6906948</v>
+        <v>6906985</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1901,19 +1772,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112038654</v>
+        <v>112038648</v>
       </c>
       <c r="B13" t="n">
-        <v>90827</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1941,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620657</v>
+        <v>620685</v>
       </c>
       <c r="R13" t="n">
-        <v>6907111</v>
+        <v>6906886</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,15 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112038640</v>
+        <v>127290459</v>
       </c>
       <c r="B14" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,34 +1880,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620639</v>
+        <v>620682</v>
       </c>
       <c r="R14" t="n">
-        <v>6906935</v>
+        <v>6906909</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,12 +1943,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,50 +1985,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112038649</v>
+        <v>127290877</v>
       </c>
       <c r="B15" t="n">
-        <v>92003</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2058</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620727</v>
+        <v>620729</v>
       </c>
       <c r="R15" t="n">
-        <v>6906958</v>
+        <v>6906963</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2175,12 +2050,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,15 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112038652</v>
+        <v>112038640</v>
       </c>
       <c r="B16" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,21 +2103,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620718</v>
+        <v>620639</v>
       </c>
       <c r="R16" t="n">
-        <v>6906985</v>
+        <v>6906935</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2309,15 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112038651</v>
+        <v>112038639</v>
       </c>
       <c r="B17" t="n">
-        <v>96736</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620706</v>
+        <v>620641</v>
       </c>
       <c r="R17" t="n">
-        <v>6906970</v>
+        <v>6906939</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2411,37 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112038655</v>
+        <v>112038643</v>
       </c>
       <c r="B18" t="n">
-        <v>90859</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2451,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620658</v>
+        <v>620644</v>
       </c>
       <c r="R18" t="n">
-        <v>6907141</v>
+        <v>6906827</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2513,37 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112038656</v>
+        <v>112038651</v>
       </c>
       <c r="B19" t="n">
-        <v>89115</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620484</v>
+        <v>620706</v>
       </c>
       <c r="R19" t="n">
-        <v>6907328</v>
+        <v>6906970</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2615,15 +2480,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112038648</v>
+        <v>112038638</v>
       </c>
       <c r="B20" t="n">
-        <v>90827</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,21 +2491,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620684</v>
+        <v>620639</v>
       </c>
       <c r="R20" t="n">
-        <v>6906886</v>
+        <v>6906948</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,50 +2577,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112038641</v>
+        <v>112038645</v>
       </c>
       <c r="B21" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620633</v>
+        <v>620658</v>
       </c>
       <c r="R21" t="n">
-        <v>6906857</v>
+        <v>6906850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2801,6 +2660,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2819,15 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112038637</v>
+        <v>102531648</v>
       </c>
       <c r="B22" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,37 +2690,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620637</v>
+        <v>620615</v>
       </c>
       <c r="R22" t="n">
-        <v>6906943</v>
+        <v>6907147</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2889,12 +2747,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2903,6 +2761,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2921,54 +2780,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112038645</v>
+        <v>113018043</v>
       </c>
       <c r="B23" t="n">
-        <v>96771</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223621</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620659</v>
+        <v>620645</v>
       </c>
       <c r="R23" t="n">
-        <v>6906849</v>
+        <v>6907289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2995,12 +2845,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,7 +2859,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3028,15 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112038646</v>
+        <v>113018045</v>
       </c>
       <c r="B24" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,21 +2888,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3068,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620674</v>
+        <v>620337</v>
       </c>
       <c r="R24" t="n">
-        <v>6906875</v>
+        <v>6907443</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3098,12 +2942,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3130,15 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113018040</v>
+        <v>132627017</v>
       </c>
       <c r="B25" t="n">
-        <v>90063</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3146,21 +2985,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3170,10 +3009,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620549</v>
+        <v>620567</v>
       </c>
       <c r="R25" t="n">
-        <v>6907071</v>
+        <v>6907210</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3200,12 +3039,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,62 +3059,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113018041</v>
+        <v>133816705</v>
       </c>
       <c r="B26" t="n">
-        <v>90009</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620629</v>
+        <v>620550</v>
       </c>
       <c r="R26" t="n">
-        <v>6907066</v>
+        <v>6907041</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3302,12 +3139,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3316,6 +3153,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3334,50 +3172,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113018045</v>
+        <v>133816706</v>
       </c>
       <c r="B27" t="n">
-        <v>90045</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620338</v>
+        <v>620552</v>
       </c>
       <c r="R27" t="n">
-        <v>6907443</v>
+        <v>6907124</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3404,12 +3237,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3436,37 +3269,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113018043</v>
+        <v>132627032</v>
       </c>
       <c r="B28" t="n">
-        <v>90045</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3304,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620644</v>
+        <v>620624</v>
       </c>
       <c r="R28" t="n">
-        <v>6907290</v>
+        <v>6907248</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3506,12 +3334,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3526,27 +3354,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113018042</v>
+        <v>127291532</v>
       </c>
       <c r="B29" t="n">
-        <v>90430</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,32 +3377,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6040186</v>
+        <v>4361</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620606</v>
+        <v>620569</v>
       </c>
       <c r="R29" t="n">
-        <v>6907271</v>
+        <v>6907190</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3606,17 +3431,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3625,7 +3455,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3644,10 +3473,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127291532</v>
+        <v>112038654</v>
       </c>
       <c r="B30" t="n">
-        <v>92633</v>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3655,34 +3484,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620569</v>
+        <v>620657</v>
       </c>
       <c r="R30" t="n">
-        <v>6907190</v>
+        <v>6907111</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3709,22 +3538,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,54 +3570,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127290459</v>
+        <v>113018041</v>
       </c>
       <c r="B31" t="n">
-        <v>92659</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620682</v>
+        <v>620629</v>
       </c>
       <c r="R31" t="n">
-        <v>6906909</v>
+        <v>6907066</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3825,22 +3635,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,10 +3667,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127290877</v>
+        <v>112038656</v>
       </c>
       <c r="B32" t="n">
-        <v>92659</v>
+        <v>91443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3878,34 +3678,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>5754</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620729</v>
+        <v>620484</v>
       </c>
       <c r="R32" t="n">
-        <v>6906963</v>
+        <v>6907328</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3932,22 +3732,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,10 +3764,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127294312</v>
+        <v>127291446</v>
       </c>
       <c r="B33" t="n">
-        <v>91647</v>
+        <v>91443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,34 +3775,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>5754</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620577</v>
+        <v>620539</v>
       </c>
       <c r="R33" t="n">
-        <v>6907001</v>
+        <v>6907155</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4044,7 +3834,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4054,7 +3844,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +3871,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127294328</v>
+        <v>113018044</v>
       </c>
       <c r="B34" t="n">
-        <v>91351</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4092,34 +3882,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620577</v>
+        <v>620324</v>
       </c>
       <c r="R34" t="n">
-        <v>6907001</v>
+        <v>6907417</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4146,22 +3944,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4188,48 +3981,62 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127294306</v>
+        <v>127291750</v>
       </c>
       <c r="B35" t="n">
-        <v>91805</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Åh, Åh, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620577</v>
+        <v>620622</v>
       </c>
       <c r="R35" t="n">
-        <v>6907001</v>
+        <v>6907237</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4258,7 +4065,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4268,7 +4075,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4295,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127291750</v>
+        <v>129574821</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,34 +4130,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åh, Åh, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620622</v>
+        <v>620692</v>
       </c>
       <c r="R36" t="n">
-        <v>6907237</v>
+        <v>6907114</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4374,22 +4172,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på grov gran, långt ned på stammen med rinnande kåda</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4416,57 +4209,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129574923</v>
+        <v>132627014</v>
       </c>
       <c r="B37" t="n">
-        <v>98797</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620676</v>
+        <v>620542</v>
       </c>
       <c r="R37" t="n">
-        <v>6907043</v>
+        <v>6907069</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4490,12 +4279,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4510,22 +4299,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129576405</v>
+        <v>132627015</v>
       </c>
       <c r="B38" t="n">
-        <v>91605</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4533,37 +4322,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620599</v>
+        <v>620554</v>
       </c>
       <c r="R38" t="n">
-        <v>6906925</v>
+        <v>6907215</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4587,12 +4381,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>rikligt med ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4607,65 +4406,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129574821</v>
+        <v>102531187</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Å, Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620692</v>
+        <v>620452</v>
       </c>
       <c r="R39" t="n">
-        <v>6907114</v>
+        <v>6907058</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4689,17 +4487,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på grov gran, långt ned på stammen med rinnande kåda</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4708,6 +4501,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4726,10 +4520,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132627016</v>
+        <v>102531543</v>
       </c>
       <c r="B40" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4755,19 +4549,23 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620553</v>
+        <v>620444</v>
       </c>
       <c r="R40" t="n">
-        <v>6907206</v>
+        <v>6907301</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4791,17 +4589,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4810,28 +4603,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132627029</v>
+        <v>102531551</v>
       </c>
       <c r="B41" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4857,19 +4651,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620619</v>
+        <v>620513</v>
       </c>
       <c r="R41" t="n">
-        <v>6907297</v>
+        <v>6907417</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4893,17 +4691,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>ca 50 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4912,71 +4705,71 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132627014</v>
+        <v>102531566</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620542</v>
+        <v>620509</v>
       </c>
       <c r="R42" t="n">
-        <v>6907069</v>
+        <v>6907532</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5000,12 +4793,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5014,66 +4807,71 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132627017</v>
+        <v>102531575</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620567</v>
+        <v>620531</v>
       </c>
       <c r="R43" t="n">
-        <v>6907210</v>
+        <v>6907514</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5097,12 +4895,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5111,28 +4909,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132627031</v>
+        <v>102531588</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5158,19 +4957,23 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620645</v>
+        <v>620593</v>
       </c>
       <c r="R44" t="n">
-        <v>6907255</v>
+        <v>6907289</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5194,17 +4997,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ca 50 bladroestter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5213,28 +5011,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132627028</v>
+        <v>102531602</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5260,19 +5059,23 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620564</v>
+        <v>620635</v>
       </c>
       <c r="R45" t="n">
-        <v>6907355</v>
+        <v>6907258</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5296,17 +5099,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5315,28 +5113,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132627024</v>
+        <v>102531620</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5362,19 +5161,23 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Åh, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620566</v>
+        <v>620662</v>
       </c>
       <c r="R46" t="n">
-        <v>6907351</v>
+        <v>6907156</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5398,17 +5201,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5417,28 +5215,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132627020</v>
+        <v>129574923</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5463,17 +5262,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Å, Mpd</t>
+          <t>Å, Å, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620612</v>
+        <v>620676</v>
       </c>
       <c r="R47" t="n">
-        <v>6907283</v>
+        <v>6907043</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5500,17 +5308,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>ca 50 bladrosetter</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5525,65 +5328,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132627015</v>
+        <v>132627016</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620554</v>
+        <v>620553</v>
       </c>
       <c r="R48" t="n">
-        <v>6907215</v>
+        <v>6907206</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5617,7 +5415,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>rikligt med ringhack på tall</t>
+          <t>ca 200 bladrosetter spridda över ca 4 m2</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5644,10 +5442,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132627021</v>
+        <v>132627018</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5679,10 +5477,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620605</v>
+        <v>620569</v>
       </c>
       <c r="R49" t="n">
-        <v>6907280</v>
+        <v>6907223</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5719,7 +5517,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ca 50 bladrosetter</t>
+          <t>100 bladrosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5749,7 +5547,7 @@
         <v>132627019</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5848,10 +5646,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132627030</v>
+        <v>132627020</v>
       </c>
       <c r="B51" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5883,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620634</v>
+        <v>620612</v>
       </c>
       <c r="R51" t="n">
-        <v>6907281</v>
+        <v>6907283</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5923,7 +5721,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ca 80 bladrosetter</t>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5950,32 +5748,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132627032</v>
+        <v>132627021</v>
       </c>
       <c r="B52" t="n">
-        <v>96348</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5985,10 +5783,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620624</v>
+        <v>620605</v>
       </c>
       <c r="R52" t="n">
-        <v>6907248</v>
+        <v>6907280</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6021,6 +5819,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6047,10 +5850,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132627023</v>
+        <v>132627022</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6082,10 +5885,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620566</v>
+        <v>620576</v>
       </c>
       <c r="R53" t="n">
-        <v>6907307</v>
+        <v>6907314</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6149,10 +5952,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132627022</v>
+        <v>132627023</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6184,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620576</v>
+        <v>620566</v>
       </c>
       <c r="R54" t="n">
-        <v>6907314</v>
+        <v>6907307</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6251,10 +6054,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132627018</v>
+        <v>132627024</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6286,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620569</v>
+        <v>620566</v>
       </c>
       <c r="R55" t="n">
-        <v>6907223</v>
+        <v>6907351</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6326,7 +6129,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>100 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6353,45 +6156,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133816706</v>
+        <v>132627028</v>
       </c>
       <c r="B56" t="n">
-        <v>79905</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1353</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kulåsen, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>620552</v>
+        <v>620564</v>
       </c>
       <c r="R56" t="n">
-        <v>6907124</v>
+        <v>6907355</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6418,12 +6221,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6438,60 +6246,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133816705</v>
+        <v>132627029</v>
       </c>
       <c r="B57" t="n">
-        <v>79905</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1353</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kulåsen, Mpd</t>
+          <t>Å, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>620550</v>
+        <v>620619</v>
       </c>
       <c r="R57" t="n">
-        <v>6907041</v>
+        <v>6907297</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6518,12 +6323,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ca 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6532,22 +6342,540 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132627030</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>620634</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6907281</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>ca 80 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132627031</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>620645</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6907255</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ca 50 bladroestter</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>102531179</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Åh, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>620459</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6907069</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>113018042</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>620606</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6907271</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127292086</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Å, Å, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>620510</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6907248</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127294312</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531648</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018043</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018045</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127294328</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129576405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627017</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1579,6 +1624,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127294306</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133816705</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133816706</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1874,6 +1934,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038649</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,6 +2036,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627032</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038637</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2165,6 +2240,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038641</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2262,6 +2342,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038642</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2359,6 +2444,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038646</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,6 +2546,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038652</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2563,6 +2658,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291532</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2660,6 +2760,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038648</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2757,6 +2862,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038654</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2873,6 +2983,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127290459</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2980,6 +3095,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127290877</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3077,6 +3197,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018041</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3174,6 +3299,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038656</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3281,6 +3411,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291446</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3378,6 +3513,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038640</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3488,6 +3628,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018044</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291750</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3716,6 +3866,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574821</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3818,6 +3973,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627014</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3925,6 +4085,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627015</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4027,6 +4192,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531187</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4129,6 +4299,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531543</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4231,6 +4406,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531551</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4333,6 +4513,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531566</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4435,6 +4620,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531575</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4537,6 +4727,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531588</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4639,6 +4834,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531602</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4741,6 +4941,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531620</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4838,6 +5043,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038639</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4935,6 +5145,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038643</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5032,6 +5247,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038651</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5138,6 +5358,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574923</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5240,6 +5465,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627016</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5342,6 +5572,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627018</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5444,6 +5679,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627019</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5546,6 +5786,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627020</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5648,6 +5893,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627021</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5750,6 +6000,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627022</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5852,6 +6107,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627023</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5954,6 +6214,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627024</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6056,6 +6321,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627028</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6158,6 +6428,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627029</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6260,6 +6535,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627030</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6362,6 +6642,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132627031</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6459,6 +6744,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038638</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6561,6 +6851,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102531179</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6663,6 +6958,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038645</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6769,6 +7069,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018042</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6876,8 +7181,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127292086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>